--- a/templates/gs/pi.xlsx
+++ b/templates/gs/pi.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6550"/>
+    <workbookView windowWidth="29400" windowHeight="14100"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>GLOBALSINO PTE.LTD.</t>
   </si>
@@ -41,9 +41,6 @@
     <t>PI Number:</t>
   </si>
   <si>
-    <t>ETD (Baseline Date for FOB Term):</t>
-  </si>
-  <si>
     <t>Incoterm:</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>Actual Manufacturer Company Address</t>
   </si>
   <si>
-    <t>Number of Cartons</t>
-  </si>
-  <si>
     <t>Country of The Origin</t>
   </si>
   <si>
@@ -119,16 +113,13 @@
     <t>EX-FACTORY DATE</t>
   </si>
   <si>
-    <t xml:space="preserve">Sub-Total </t>
-  </si>
-  <si>
-    <t>TOTAL EXCLUDING EXCISE TAX  (USD)</t>
+    <t>China</t>
+  </si>
+  <si>
+    <t>Sub-Total</t>
   </si>
   <si>
     <t>Signature:</t>
-  </si>
-  <si>
-    <t>TINA</t>
   </si>
   <si>
     <t>Date:</t>
@@ -150,7 +141,7 @@
     <numFmt numFmtId="180" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="58">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -216,9 +207,39 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF00B0F0"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -809,7 +830,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -853,25 +874,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1084,320 +1092,320 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="36" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="36" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="48" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="49" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="48" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="39" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="52" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="48" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="49" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="48" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="39" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1467,50 +1475,61 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="2" borderId="2" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1525,9 +1544,12 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="10" fillId="0" borderId="2" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="2" xfId="55" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1542,6 +1564,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1552,7 +1577,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="87" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1583,25 +1608,43 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="87" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="77" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="77" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="14" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="76" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="10" fillId="2" borderId="0" xfId="76" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="180" fontId="1" fillId="2" borderId="0" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="57" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="40" fontId="1" fillId="2" borderId="4" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="0" xfId="75" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="5" xfId="99" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="87" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="75" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="87" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="87" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1769,8 +1812,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7378065" y="71755"/>
-          <a:ext cx="3866515" cy="927100"/>
+          <a:off x="5542915" y="71755"/>
+          <a:ext cx="4864100" cy="927100"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -2191,15 +2234,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.6"/>
   <cols>
     <col min="1" max="1" width="17.75" style="4" customWidth="1"/>
     <col min="2" max="2" width="13.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="10.875" style="4" customWidth="1"/>
     <col min="4" max="4" width="13.25" style="4" customWidth="1"/>
-    <col min="5" max="5" width="40" style="4" customWidth="1"/>
-    <col min="6" max="6" width="13.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="21" style="4" customWidth="1"/>
+    <col min="6" max="6" width="30.3303571428571" style="4" customWidth="1"/>
     <col min="7" max="7" width="12.5" style="4" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="4" customWidth="1"/>
     <col min="9" max="9" width="13.5" style="4" customWidth="1"/>
@@ -2264,249 +2307,273 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
     </row>
-    <row r="6" s="2" customFormat="1" ht="18" customHeight="1" spans="1:9">
+    <row r="6" s="2" customFormat="1" ht="44" customHeight="1" spans="1:9">
       <c r="A6" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
+      <c r="D6" s="22"/>
       <c r="E6" s="19"/>
-      <c r="F6" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="25"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A7" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="C7" s="27"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="22" t="s">
+      <c r="G7" s="28"/>
+      <c r="H7" s="29"/>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="27" customHeight="1" spans="1:9">
+      <c r="A8" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="26"/>
-      <c r="H7" s="24"/>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A8" s="19" t="s">
+      <c r="B8" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="C8" s="27"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="27"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="31"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A9" s="28"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
       <c r="E9" s="19"/>
-      <c r="F9" s="22"/>
+      <c r="F9" s="23"/>
       <c r="G9" s="19"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="30"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="34"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="H10" s="32"/>
-      <c r="I10" s="30"/>
+      <c r="G10" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="36"/>
+      <c r="I10" s="27"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A11" s="36"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="30"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="34"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A12" s="28"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="30"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="34"/>
     </row>
     <row r="13" s="3" customFormat="1" ht="18" customHeight="1" spans="1:9">
-      <c r="A13" s="28"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="40"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="44"/>
       <c r="G13" s="19"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="30"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="34"/>
     </row>
     <row r="14" s="3" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A14" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="47"/>
     </row>
     <row r="15" s="3" customFormat="1" ht="21.95" customHeight="1" spans="1:9">
       <c r="A15" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="47"/>
     </row>
     <row r="16" s="3" customFormat="1" ht="21.95" customHeight="1" spans="1:9">
-      <c r="A16" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="47"/>
     </row>
     <row r="17" s="3" customFormat="1" ht="21.95" customHeight="1" spans="1:9">
-      <c r="A17" s="28"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
     </row>
     <row r="18" ht="15.95" customHeight="1" spans="1:9">
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:9">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="50" t="s">
+      <c r="D19" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="E19" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="51" t="s">
+      <c r="F19" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="52" t="s">
+      <c r="G19" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="F19" s="53" t="s">
+      <c r="H19" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="51" t="s">
+      <c r="I19" s="60" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="54" t="s">
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:9">
+      <c r="A20" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="55" t="s">
-        <v>29</v>
-      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="63"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="31"/>
     </row>
-    <row r="20" ht="15.95" customHeight="1" spans="1:9">
-      <c r="A20" s="49"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="F20" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" s="57"/>
-      <c r="H20" s="58"/>
+    <row r="21" ht="28" customHeight="1" spans="1:9">
+      <c r="A21" s="54"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="68"/>
     </row>
-    <row r="21" ht="15.95" customHeight="1" spans="1:9">
-      <c r="A21" s="49"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="G21" s="59" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="60"/>
+    <row r="22" ht="28" customHeight="1" spans="1:9">
+      <c r="A22" s="54"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="68"/>
     </row>
-    <row r="22" ht="15.95" customHeight="1"/>
-    <row r="23" ht="15.95" customHeight="1" spans="1:9">
-      <c r="A23" s="1"/>
-      <c r="F23" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="62"/>
+    <row r="23" ht="28" customHeight="1" spans="1:9">
+      <c r="A23" s="54"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="68"/>
     </row>
     <row r="24" ht="15.95" customHeight="1" spans="1:9">
-      <c r="A24" s="1"/>
-      <c r="F24" s="63" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" s="23"/>
-      <c r="H24" s="64"/>
+      <c r="F24" s="70" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+    </row>
+    <row r="25" ht="15.95" customHeight="1" spans="1:9">
+      <c r="A25" s="1"/>
+      <c r="F25" s="72" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="73"/>
+    </row>
+    <row r="26" ht="15.95" customHeight="1" spans="1:9">
+      <c r="A26" s="1"/>
+      <c r="F26" s="74" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" s="28"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I14:I16"/>
     <mergeCell ref="A2:D3"/>
     <mergeCell ref="F1:I4"/>
   </mergeCells>
